--- a/src/assets/schoolDesk/bdd/bdd build.xlsx
+++ b/src/assets/schoolDesk/bdd/bdd build.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MAMP\htdocs\Rugby-Academy\src\assets\schoolDesk\bdd\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AB5B7341-0FAD-4365-952D-88939D86E44B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5AB8BD9-5425-41CB-B358-11E349158574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{F8B8C4F5-9CBE-45C8-9BFD-685DE0AE8ED2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="58">
   <si>
     <t>role</t>
   </si>
@@ -174,13 +174,44 @@
     <t>user_role</t>
   </si>
   <si>
-    <t>user_role : ligne club_id</t>
-  </si>
-  <si>
     <t>user_role : ligne role_id</t>
   </si>
   <si>
     <t>user_role : ligne user_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trombinoscope_group </t>
+  </si>
+  <si>
+    <t>group_id</t>
+  </si>
+  <si>
+    <t>position</t>
+  </si>
+  <si>
+    <t>club : ligne club_id</t>
+  </si>
+  <si>
+    <t>user_role : ligne club_id
+trombinoscope_group : ligne club_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trombinoscope_card </t>
+  </si>
+  <si>
+    <t>card_id</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>photo</t>
+  </si>
+  <si>
+    <t>trombinoscope_group : ligne groupe_id</t>
+  </si>
+  <si>
+    <t>trombinoscope_card : ligne groupe_id</t>
   </si>
 </sst>
 </file>
@@ -242,7 +273,79 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="48">
+  <dxfs count="72">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -401,76 +504,114 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F7B9363E-452E-4289-93FC-70886BD6D8FB}" name="Tableau2" displayName="Tableau2" ref="B3:K5" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F7B9363E-452E-4289-93FC-70886BD6D8FB}" name="Tableau2" displayName="Tableau2" ref="B3:K5" totalsRowShown="0" headerRowDxfId="71" dataDxfId="70">
   <autoFilter ref="B3:K5" xr:uid="{F7B9363E-452E-4289-93FC-70886BD6D8FB}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{DB4C2CD3-3231-4168-9A87-457D5664083E}" name="nom table" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{2192C049-1AEB-4E35-A091-A07CC91CD244}" name="nom colonne" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{F58F956B-23A5-44DC-B56B-F9B8C56B2423}" name="type" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{85757BEB-9E58-4E89-80B5-049A5B671907}" name="Interclassement" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{AAA0C635-0F93-4AF6-B139-362C2718F431}" name="Attributs" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{077C9FE2-0A59-49FB-9CC1-7902F968C636}" name="Null" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{D3497013-3EF1-42FD-8060-211DD3868C03}" name="Valeur par défaut" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{407A762B-C81E-4389-87AC-0043C1E43AA0}" name="(clé étrangère) Pointe vers" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{5B40F928-777F-4FB3-BCBE-58A5C477C95E}" name="Est pointé depuis" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{EE04D510-1207-48EF-ADAB-C32FA84C32DF}" name="Extra2" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{DB4C2CD3-3231-4168-9A87-457D5664083E}" name="nom table" dataDxfId="69"/>
+    <tableColumn id="2" xr3:uid="{2192C049-1AEB-4E35-A091-A07CC91CD244}" name="nom colonne" dataDxfId="68"/>
+    <tableColumn id="3" xr3:uid="{F58F956B-23A5-44DC-B56B-F9B8C56B2423}" name="type" dataDxfId="67"/>
+    <tableColumn id="4" xr3:uid="{85757BEB-9E58-4E89-80B5-049A5B671907}" name="Interclassement" dataDxfId="66"/>
+    <tableColumn id="5" xr3:uid="{AAA0C635-0F93-4AF6-B139-362C2718F431}" name="Attributs" dataDxfId="65"/>
+    <tableColumn id="6" xr3:uid="{077C9FE2-0A59-49FB-9CC1-7902F968C636}" name="Null" dataDxfId="64"/>
+    <tableColumn id="7" xr3:uid="{D3497013-3EF1-42FD-8060-211DD3868C03}" name="Valeur par défaut" dataDxfId="63"/>
+    <tableColumn id="8" xr3:uid="{407A762B-C81E-4389-87AC-0043C1E43AA0}" name="(clé étrangère) Pointe vers" dataDxfId="62"/>
+    <tableColumn id="9" xr3:uid="{5B40F928-777F-4FB3-BCBE-58A5C477C95E}" name="Est pointé depuis" dataDxfId="61"/>
+    <tableColumn id="10" xr3:uid="{EE04D510-1207-48EF-ADAB-C32FA84C32DF}" name="Extra2" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A2B3D216-B0BE-46DB-98BB-EBFCF643F6EF}" name="Tableau24" displayName="Tableau24" ref="B8:K16" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A2B3D216-B0BE-46DB-98BB-EBFCF643F6EF}" name="Tableau24" displayName="Tableau24" ref="B8:K16" totalsRowShown="0" headerRowDxfId="59" dataDxfId="58">
   <autoFilter ref="B8:K16" xr:uid="{A2B3D216-B0BE-46DB-98BB-EBFCF643F6EF}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{15666A47-A6B0-4E0A-91AE-FB891679101B}" name="nom table" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{DFE8A646-5A6E-4382-A318-898309162AC6}" name="nom colonne" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{8161E4A6-BFC8-48E5-A144-897DC62F3CD6}" name="type" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{3F224333-E92F-4D3F-A895-7E8F8E63E833}" name="Interclassement" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{DADBA23C-D744-4CAA-8819-137469AF5DF5}" name="Attributs" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{7B36E0F4-12E1-4F86-BC0D-560A0F7ADA4A}" name="Null" dataDxfId="40"/>
-    <tableColumn id="7" xr3:uid="{099F1013-33FB-4C84-9B53-8F62353BADAC}" name="Valeur par défaut" dataDxfId="39"/>
-    <tableColumn id="8" xr3:uid="{83232AFE-D729-4180-B284-3864FAEC2CD3}" name="(clé étrangère) Pointe vers" dataDxfId="38"/>
-    <tableColumn id="9" xr3:uid="{944CFF04-1EFE-4C94-BF04-99759F88C2DC}" name="Est pointé depuis" dataDxfId="24"/>
-    <tableColumn id="10" xr3:uid="{6882D6F5-62FC-400C-AC09-0100987362DD}" name="Extra2" dataDxfId="27"/>
+    <tableColumn id="1" xr3:uid="{15666A47-A6B0-4E0A-91AE-FB891679101B}" name="nom table" dataDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{DFE8A646-5A6E-4382-A318-898309162AC6}" name="nom colonne" dataDxfId="56"/>
+    <tableColumn id="3" xr3:uid="{8161E4A6-BFC8-48E5-A144-897DC62F3CD6}" name="type" dataDxfId="55"/>
+    <tableColumn id="4" xr3:uid="{3F224333-E92F-4D3F-A895-7E8F8E63E833}" name="Interclassement" dataDxfId="54"/>
+    <tableColumn id="5" xr3:uid="{DADBA23C-D744-4CAA-8819-137469AF5DF5}" name="Attributs" dataDxfId="53"/>
+    <tableColumn id="6" xr3:uid="{7B36E0F4-12E1-4F86-BC0D-560A0F7ADA4A}" name="Null" dataDxfId="52"/>
+    <tableColumn id="7" xr3:uid="{099F1013-33FB-4C84-9B53-8F62353BADAC}" name="Valeur par défaut" dataDxfId="51"/>
+    <tableColumn id="8" xr3:uid="{83232AFE-D729-4180-B284-3864FAEC2CD3}" name="(clé étrangère) Pointe vers" dataDxfId="50"/>
+    <tableColumn id="9" xr3:uid="{944CFF04-1EFE-4C94-BF04-99759F88C2DC}" name="Est pointé depuis" dataDxfId="49"/>
+    <tableColumn id="10" xr3:uid="{6882D6F5-62FC-400C-AC09-0100987362DD}" name="Extra2" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4988D469-AD98-46C4-88D3-4A641744DA50}" name="Tableau25" displayName="Tableau25" ref="B19:K22" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4988D469-AD98-46C4-88D3-4A641744DA50}" name="Tableau25" displayName="Tableau25" ref="B19:K22" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
   <autoFilter ref="B19:K22" xr:uid="{4988D469-AD98-46C4-88D3-4A641744DA50}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{02BB2D94-0C11-489C-A941-D935E51FCC2F}" name="nom table" dataDxfId="37"/>
-    <tableColumn id="2" xr3:uid="{03FD9E41-50D8-4886-B21D-58D99087C0C9}" name="nom colonne" dataDxfId="36"/>
-    <tableColumn id="3" xr3:uid="{114AB77E-D5C9-4EDA-92E5-F821A0B6289B}" name="type" dataDxfId="35"/>
-    <tableColumn id="4" xr3:uid="{35482F0D-880F-41BE-9603-A05C9DCE73A9}" name="Interclassement" dataDxfId="34"/>
-    <tableColumn id="5" xr3:uid="{A0A47C94-BF2A-4E1E-A050-21842B13386A}" name="Attributs" dataDxfId="33"/>
-    <tableColumn id="6" xr3:uid="{F45F8180-9A05-49A5-8C33-B48EBE3B0157}" name="Null" dataDxfId="32"/>
-    <tableColumn id="7" xr3:uid="{CBC3CADB-CB55-4F26-9EC5-DB274703AF01}" name="Valeur par défaut" dataDxfId="31"/>
-    <tableColumn id="8" xr3:uid="{A4F19A0E-1B3E-4E3B-88D9-7327DA24E71D}" name="(clé étrangère) Pointe vers" dataDxfId="30"/>
-    <tableColumn id="9" xr3:uid="{699699A2-A73C-4C59-8354-C04B358C6913}" name="Est pointé depuis" dataDxfId="25"/>
-    <tableColumn id="10" xr3:uid="{E8A1F3E0-9FFC-4D33-887C-6A0EFECEDE8B}" name="Extra2" dataDxfId="26"/>
+    <tableColumn id="1" xr3:uid="{02BB2D94-0C11-489C-A941-D935E51FCC2F}" name="nom table" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{03FD9E41-50D8-4886-B21D-58D99087C0C9}" name="nom colonne" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{114AB77E-D5C9-4EDA-92E5-F821A0B6289B}" name="type" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{35482F0D-880F-41BE-9603-A05C9DCE73A9}" name="Interclassement" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{A0A47C94-BF2A-4E1E-A050-21842B13386A}" name="Attributs" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{F45F8180-9A05-49A5-8C33-B48EBE3B0157}" name="Null" dataDxfId="40"/>
+    <tableColumn id="7" xr3:uid="{CBC3CADB-CB55-4F26-9EC5-DB274703AF01}" name="Valeur par défaut" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{A4F19A0E-1B3E-4E3B-88D9-7327DA24E71D}" name="(clé étrangère) Pointe vers" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{699699A2-A73C-4C59-8354-C04B358C6913}" name="Est pointé depuis" dataDxfId="37"/>
+    <tableColumn id="10" xr3:uid="{E8A1F3E0-9FFC-4D33-887C-6A0EFECEDE8B}" name="Extra2" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{FCA9C960-1AA3-4F83-BE30-98ED09E60E09}" name="Tableau26" displayName="Tableau26" ref="B25:K30" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{FCA9C960-1AA3-4F83-BE30-98ED09E60E09}" name="Tableau26" displayName="Tableau26" ref="B25:K30" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
   <autoFilter ref="B25:K30" xr:uid="{FCA9C960-1AA3-4F83-BE30-98ED09E60E09}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{9AE8E965-0B21-468D-814D-9FD22A09D2B0}" name="nom table" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{908A4D0E-C232-43D4-BCF1-D888DBDD0BA1}" name="nom colonne" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{72BE23E7-4BEC-4486-9A9D-516D8C1E60E1}" name="type" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{B71E94CD-95C7-4728-B535-41CEAFE3AE18}" name="Interclassement" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{A16B840B-0CE8-4726-972C-84FAE671FF92}" name="Attributs" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{79FE67FC-68D7-49FF-9EDC-88E046C1D212}" name="Null" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{2FF80A13-5FA3-49A7-BAB0-B732F814C1F4}" name="Valeur par défaut" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{1569FBC2-03BC-4E35-8636-E0826A5659BE}" name="(clé étrangère) Pointe vers" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{FD191C2C-D2F4-46AF-8433-18181AB3F030}" name="Est pointé depuis" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{05A97718-549F-40F2-BE8D-64C699D2680F}" name="Extra2" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{9AE8E965-0B21-468D-814D-9FD22A09D2B0}" name="nom table" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{908A4D0E-C232-43D4-BCF1-D888DBDD0BA1}" name="nom colonne" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{72BE23E7-4BEC-4486-9A9D-516D8C1E60E1}" name="type" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{B71E94CD-95C7-4728-B535-41CEAFE3AE18}" name="Interclassement" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{A16B840B-0CE8-4726-972C-84FAE671FF92}" name="Attributs" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{79FE67FC-68D7-49FF-9EDC-88E046C1D212}" name="Null" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{2FF80A13-5FA3-49A7-BAB0-B732F814C1F4}" name="Valeur par défaut" dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{1569FBC2-03BC-4E35-8636-E0826A5659BE}" name="(clé étrangère) Pointe vers" dataDxfId="26"/>
+    <tableColumn id="9" xr3:uid="{FD191C2C-D2F4-46AF-8433-18181AB3F030}" name="Est pointé depuis" dataDxfId="25"/>
+    <tableColumn id="10" xr3:uid="{05A97718-549F-40F2-BE8D-64C699D2680F}" name="Extra2" dataDxfId="24"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B2130637-D823-466F-9E7C-A0B2974DBAB9}" name="Tableau262" displayName="Tableau262" ref="B33:K37" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+  <autoFilter ref="B33:K37" xr:uid="{B2130637-D823-466F-9E7C-A0B2974DBAB9}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{3B8F7F72-A334-4A49-BEE0-D13E23F3E3CC}" name="nom table" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{AEB3CC68-42FB-4348-BC29-FF88B0E3E32F}" name="nom colonne" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{FDB27E46-F3D7-4AD3-8C8E-38CCF3BACC40}" name="type" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{586C31D4-499E-4F13-B384-12E98B0846B0}" name="Interclassement" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{F8C8E00A-85CA-4E4D-A981-2D224A007457}" name="Attributs" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{CC2360D5-0BE6-46A3-8F52-92DAC95DA8C5}" name="Null" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{220E2022-11C7-4541-94F2-61F18AA75412}" name="Valeur par défaut" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{3D6C0E02-E889-4F1E-B8E8-0E6D79A326CB}" name="(clé étrangère) Pointe vers" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{1923CC31-7C4A-4F33-AF1C-81A17636208D}" name="Est pointé depuis" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{CEBB73E6-8AD0-4EB7-A512-9EBF052F98A0}" name="Extra2" dataDxfId="12"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{4A46F6C2-25B0-4B2E-AFF2-D7A152F2D085}" name="Tableau2627" displayName="Tableau2627" ref="B40:K46" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="B40:K46" xr:uid="{4A46F6C2-25B0-4B2E-AFF2-D7A152F2D085}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{B0196D0D-4EE9-4669-B58D-8221FA31729C}" name="nom table" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{339D5E01-998A-4D41-A541-124611D984EA}" name="nom colonne" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{E4968142-9B29-4C13-95AE-65FAABE5E344}" name="type" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{3F85CB82-F3FF-42F2-9F2F-B6D9B52BE9EA}" name="Interclassement" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{FC709251-65F8-45D7-908E-93A303D53C8C}" name="Attributs" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{61A4ECD6-1666-4AB5-9F5A-8171206B2065}" name="Null" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{3B57F620-CD26-4A82-91BD-8477C3480807}" name="Valeur par défaut" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{FB067A86-938C-43E4-B4EE-E7F0FEF35F81}" name="(clé étrangère) Pointe vers" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{F44CB662-EB1D-44EA-B201-869A9416FCED}" name="Est pointé depuis" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{EBA54CB5-27B4-49A3-8F65-D5FD1AEA140D}" name="Extra2" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -793,16 +934,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{540E0E48-FC0C-42DF-90F9-8F82C39FB181}">
-  <dimension ref="B2:K30"/>
+  <dimension ref="B2:K46"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="1"/>
-    <col min="2" max="4" width="17.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="44.7109375" style="1" customWidth="1"/>
+    <col min="3" max="4" width="17.42578125" style="1" customWidth="1"/>
     <col min="5" max="5" width="20.28515625" style="1" customWidth="1"/>
     <col min="6" max="7" width="17.42578125" style="1" customWidth="1"/>
     <col min="8" max="8" width="22" style="1" customWidth="1"/>
     <col min="9" max="10" width="43.42578125" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="11.42578125" style="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -871,7 +1014,7 @@
         <v>11</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>29</v>
@@ -966,7 +1109,7 @@
         <v>11</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>29</v>
@@ -1282,7 +1425,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>33</v>
       </c>
@@ -1302,7 +1445,7 @@
         <v>11</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>29</v>
@@ -1379,19 +1522,327 @@
         <v>40</v>
       </c>
     </row>
+    <row r="32" spans="2:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B34" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B35" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B36" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B37" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B41" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B42" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B44" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G45" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
+    <mergeCell ref="B39:K39"/>
     <mergeCell ref="B24:K24"/>
     <mergeCell ref="B18:K18"/>
     <mergeCell ref="B7:K7"/>
     <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B32:K32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="4">
+  <tableParts count="6">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
   </tableParts>
 </worksheet>
 </file>
--- a/src/assets/schoolDesk/bdd/bdd build.xlsx
+++ b/src/assets/schoolDesk/bdd/bdd build.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MAMP\htdocs\Rugby-Academy\src\assets\schoolDesk\bdd\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5AB8BD9-5425-41CB-B358-11E349158574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00BB3908-7EC2-4F9B-96F0-7041F7D86A9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{F8B8C4F5-9CBE-45C8-9BFD-685DE0AE8ED2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="63">
   <si>
     <t>role</t>
   </si>
@@ -192,26 +192,42 @@
     <t>club : ligne club_id</t>
   </si>
   <si>
+    <t xml:space="preserve">trombinoscope_card </t>
+  </si>
+  <si>
+    <t>card_id</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>photo</t>
+  </si>
+  <si>
+    <t>trombinoscope_group : ligne groupe_id</t>
+  </si>
+  <si>
+    <t>trombinoscope_card : ligne groupe_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">structure_group </t>
+  </si>
+  <si>
+    <t xml:space="preserve">structure_card </t>
+  </si>
+  <si>
+    <t>TEXT</t>
+  </si>
+  <si>
     <t>user_role : ligne club_id
-trombinoscope_group : ligne club_id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">trombinoscope_card </t>
-  </si>
-  <si>
-    <t>card_id</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>photo</t>
-  </si>
-  <si>
-    <t>trombinoscope_group : ligne groupe_id</t>
-  </si>
-  <si>
-    <t>trombinoscope_card : ligne groupe_id</t>
+trombinoscope_group : ligne club_id
+structure_group  : ligne club_id</t>
+  </si>
+  <si>
+    <t>structure_group : ligne groupe_id</t>
+  </si>
+  <si>
+    <t>structure_card : ligne groupe_id</t>
   </si>
 </sst>
 </file>
@@ -273,7 +289,79 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="72">
+  <dxfs count="96">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -504,114 +592,152 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F7B9363E-452E-4289-93FC-70886BD6D8FB}" name="Tableau2" displayName="Tableau2" ref="B3:K5" totalsRowShown="0" headerRowDxfId="71" dataDxfId="70">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F7B9363E-452E-4289-93FC-70886BD6D8FB}" name="Tableau2" displayName="Tableau2" ref="B3:K5" totalsRowShown="0" headerRowDxfId="95" dataDxfId="94">
   <autoFilter ref="B3:K5" xr:uid="{F7B9363E-452E-4289-93FC-70886BD6D8FB}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{DB4C2CD3-3231-4168-9A87-457D5664083E}" name="nom table" dataDxfId="69"/>
-    <tableColumn id="2" xr3:uid="{2192C049-1AEB-4E35-A091-A07CC91CD244}" name="nom colonne" dataDxfId="68"/>
-    <tableColumn id="3" xr3:uid="{F58F956B-23A5-44DC-B56B-F9B8C56B2423}" name="type" dataDxfId="67"/>
-    <tableColumn id="4" xr3:uid="{85757BEB-9E58-4E89-80B5-049A5B671907}" name="Interclassement" dataDxfId="66"/>
-    <tableColumn id="5" xr3:uid="{AAA0C635-0F93-4AF6-B139-362C2718F431}" name="Attributs" dataDxfId="65"/>
-    <tableColumn id="6" xr3:uid="{077C9FE2-0A59-49FB-9CC1-7902F968C636}" name="Null" dataDxfId="64"/>
-    <tableColumn id="7" xr3:uid="{D3497013-3EF1-42FD-8060-211DD3868C03}" name="Valeur par défaut" dataDxfId="63"/>
-    <tableColumn id="8" xr3:uid="{407A762B-C81E-4389-87AC-0043C1E43AA0}" name="(clé étrangère) Pointe vers" dataDxfId="62"/>
-    <tableColumn id="9" xr3:uid="{5B40F928-777F-4FB3-BCBE-58A5C477C95E}" name="Est pointé depuis" dataDxfId="61"/>
-    <tableColumn id="10" xr3:uid="{EE04D510-1207-48EF-ADAB-C32FA84C32DF}" name="Extra2" dataDxfId="60"/>
+    <tableColumn id="1" xr3:uid="{DB4C2CD3-3231-4168-9A87-457D5664083E}" name="nom table" dataDxfId="93"/>
+    <tableColumn id="2" xr3:uid="{2192C049-1AEB-4E35-A091-A07CC91CD244}" name="nom colonne" dataDxfId="92"/>
+    <tableColumn id="3" xr3:uid="{F58F956B-23A5-44DC-B56B-F9B8C56B2423}" name="type" dataDxfId="91"/>
+    <tableColumn id="4" xr3:uid="{85757BEB-9E58-4E89-80B5-049A5B671907}" name="Interclassement" dataDxfId="90"/>
+    <tableColumn id="5" xr3:uid="{AAA0C635-0F93-4AF6-B139-362C2718F431}" name="Attributs" dataDxfId="89"/>
+    <tableColumn id="6" xr3:uid="{077C9FE2-0A59-49FB-9CC1-7902F968C636}" name="Null" dataDxfId="88"/>
+    <tableColumn id="7" xr3:uid="{D3497013-3EF1-42FD-8060-211DD3868C03}" name="Valeur par défaut" dataDxfId="87"/>
+    <tableColumn id="8" xr3:uid="{407A762B-C81E-4389-87AC-0043C1E43AA0}" name="(clé étrangère) Pointe vers" dataDxfId="86"/>
+    <tableColumn id="9" xr3:uid="{5B40F928-777F-4FB3-BCBE-58A5C477C95E}" name="Est pointé depuis" dataDxfId="85"/>
+    <tableColumn id="10" xr3:uid="{EE04D510-1207-48EF-ADAB-C32FA84C32DF}" name="Extra2" dataDxfId="84"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A2B3D216-B0BE-46DB-98BB-EBFCF643F6EF}" name="Tableau24" displayName="Tableau24" ref="B8:K16" totalsRowShown="0" headerRowDxfId="59" dataDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A2B3D216-B0BE-46DB-98BB-EBFCF643F6EF}" name="Tableau24" displayName="Tableau24" ref="B8:K16" totalsRowShown="0" headerRowDxfId="83" dataDxfId="82">
   <autoFilter ref="B8:K16" xr:uid="{A2B3D216-B0BE-46DB-98BB-EBFCF643F6EF}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{15666A47-A6B0-4E0A-91AE-FB891679101B}" name="nom table" dataDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{DFE8A646-5A6E-4382-A318-898309162AC6}" name="nom colonne" dataDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{8161E4A6-BFC8-48E5-A144-897DC62F3CD6}" name="type" dataDxfId="55"/>
-    <tableColumn id="4" xr3:uid="{3F224333-E92F-4D3F-A895-7E8F8E63E833}" name="Interclassement" dataDxfId="54"/>
-    <tableColumn id="5" xr3:uid="{DADBA23C-D744-4CAA-8819-137469AF5DF5}" name="Attributs" dataDxfId="53"/>
-    <tableColumn id="6" xr3:uid="{7B36E0F4-12E1-4F86-BC0D-560A0F7ADA4A}" name="Null" dataDxfId="52"/>
-    <tableColumn id="7" xr3:uid="{099F1013-33FB-4C84-9B53-8F62353BADAC}" name="Valeur par défaut" dataDxfId="51"/>
-    <tableColumn id="8" xr3:uid="{83232AFE-D729-4180-B284-3864FAEC2CD3}" name="(clé étrangère) Pointe vers" dataDxfId="50"/>
-    <tableColumn id="9" xr3:uid="{944CFF04-1EFE-4C94-BF04-99759F88C2DC}" name="Est pointé depuis" dataDxfId="49"/>
-    <tableColumn id="10" xr3:uid="{6882D6F5-62FC-400C-AC09-0100987362DD}" name="Extra2" dataDxfId="48"/>
+    <tableColumn id="1" xr3:uid="{15666A47-A6B0-4E0A-91AE-FB891679101B}" name="nom table" dataDxfId="81"/>
+    <tableColumn id="2" xr3:uid="{DFE8A646-5A6E-4382-A318-898309162AC6}" name="nom colonne" dataDxfId="80"/>
+    <tableColumn id="3" xr3:uid="{8161E4A6-BFC8-48E5-A144-897DC62F3CD6}" name="type" dataDxfId="79"/>
+    <tableColumn id="4" xr3:uid="{3F224333-E92F-4D3F-A895-7E8F8E63E833}" name="Interclassement" dataDxfId="78"/>
+    <tableColumn id="5" xr3:uid="{DADBA23C-D744-4CAA-8819-137469AF5DF5}" name="Attributs" dataDxfId="77"/>
+    <tableColumn id="6" xr3:uid="{7B36E0F4-12E1-4F86-BC0D-560A0F7ADA4A}" name="Null" dataDxfId="76"/>
+    <tableColumn id="7" xr3:uid="{099F1013-33FB-4C84-9B53-8F62353BADAC}" name="Valeur par défaut" dataDxfId="75"/>
+    <tableColumn id="8" xr3:uid="{83232AFE-D729-4180-B284-3864FAEC2CD3}" name="(clé étrangère) Pointe vers" dataDxfId="74"/>
+    <tableColumn id="9" xr3:uid="{944CFF04-1EFE-4C94-BF04-99759F88C2DC}" name="Est pointé depuis" dataDxfId="73"/>
+    <tableColumn id="10" xr3:uid="{6882D6F5-62FC-400C-AC09-0100987362DD}" name="Extra2" dataDxfId="72"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4988D469-AD98-46C4-88D3-4A641744DA50}" name="Tableau25" displayName="Tableau25" ref="B19:K22" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4988D469-AD98-46C4-88D3-4A641744DA50}" name="Tableau25" displayName="Tableau25" ref="B19:K22" totalsRowShown="0" headerRowDxfId="71" dataDxfId="70">
   <autoFilter ref="B19:K22" xr:uid="{4988D469-AD98-46C4-88D3-4A641744DA50}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{02BB2D94-0C11-489C-A941-D935E51FCC2F}" name="nom table" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{03FD9E41-50D8-4886-B21D-58D99087C0C9}" name="nom colonne" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{114AB77E-D5C9-4EDA-92E5-F821A0B6289B}" name="type" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{35482F0D-880F-41BE-9603-A05C9DCE73A9}" name="Interclassement" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{A0A47C94-BF2A-4E1E-A050-21842B13386A}" name="Attributs" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{F45F8180-9A05-49A5-8C33-B48EBE3B0157}" name="Null" dataDxfId="40"/>
-    <tableColumn id="7" xr3:uid="{CBC3CADB-CB55-4F26-9EC5-DB274703AF01}" name="Valeur par défaut" dataDxfId="39"/>
-    <tableColumn id="8" xr3:uid="{A4F19A0E-1B3E-4E3B-88D9-7327DA24E71D}" name="(clé étrangère) Pointe vers" dataDxfId="38"/>
-    <tableColumn id="9" xr3:uid="{699699A2-A73C-4C59-8354-C04B358C6913}" name="Est pointé depuis" dataDxfId="37"/>
-    <tableColumn id="10" xr3:uid="{E8A1F3E0-9FFC-4D33-887C-6A0EFECEDE8B}" name="Extra2" dataDxfId="36"/>
+    <tableColumn id="1" xr3:uid="{02BB2D94-0C11-489C-A941-D935E51FCC2F}" name="nom table" dataDxfId="69"/>
+    <tableColumn id="2" xr3:uid="{03FD9E41-50D8-4886-B21D-58D99087C0C9}" name="nom colonne" dataDxfId="68"/>
+    <tableColumn id="3" xr3:uid="{114AB77E-D5C9-4EDA-92E5-F821A0B6289B}" name="type" dataDxfId="67"/>
+    <tableColumn id="4" xr3:uid="{35482F0D-880F-41BE-9603-A05C9DCE73A9}" name="Interclassement" dataDxfId="66"/>
+    <tableColumn id="5" xr3:uid="{A0A47C94-BF2A-4E1E-A050-21842B13386A}" name="Attributs" dataDxfId="65"/>
+    <tableColumn id="6" xr3:uid="{F45F8180-9A05-49A5-8C33-B48EBE3B0157}" name="Null" dataDxfId="64"/>
+    <tableColumn id="7" xr3:uid="{CBC3CADB-CB55-4F26-9EC5-DB274703AF01}" name="Valeur par défaut" dataDxfId="63"/>
+    <tableColumn id="8" xr3:uid="{A4F19A0E-1B3E-4E3B-88D9-7327DA24E71D}" name="(clé étrangère) Pointe vers" dataDxfId="62"/>
+    <tableColumn id="9" xr3:uid="{699699A2-A73C-4C59-8354-C04B358C6913}" name="Est pointé depuis" dataDxfId="61"/>
+    <tableColumn id="10" xr3:uid="{E8A1F3E0-9FFC-4D33-887C-6A0EFECEDE8B}" name="Extra2" dataDxfId="60"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{FCA9C960-1AA3-4F83-BE30-98ED09E60E09}" name="Tableau26" displayName="Tableau26" ref="B25:K30" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{FCA9C960-1AA3-4F83-BE30-98ED09E60E09}" name="Tableau26" displayName="Tableau26" ref="B25:K30" totalsRowShown="0" headerRowDxfId="59" dataDxfId="58">
   <autoFilter ref="B25:K30" xr:uid="{FCA9C960-1AA3-4F83-BE30-98ED09E60E09}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{9AE8E965-0B21-468D-814D-9FD22A09D2B0}" name="nom table" dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{908A4D0E-C232-43D4-BCF1-D888DBDD0BA1}" name="nom colonne" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{72BE23E7-4BEC-4486-9A9D-516D8C1E60E1}" name="type" dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{B71E94CD-95C7-4728-B535-41CEAFE3AE18}" name="Interclassement" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{A16B840B-0CE8-4726-972C-84FAE671FF92}" name="Attributs" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{79FE67FC-68D7-49FF-9EDC-88E046C1D212}" name="Null" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{2FF80A13-5FA3-49A7-BAB0-B732F814C1F4}" name="Valeur par défaut" dataDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{1569FBC2-03BC-4E35-8636-E0826A5659BE}" name="(clé étrangère) Pointe vers" dataDxfId="26"/>
-    <tableColumn id="9" xr3:uid="{FD191C2C-D2F4-46AF-8433-18181AB3F030}" name="Est pointé depuis" dataDxfId="25"/>
-    <tableColumn id="10" xr3:uid="{05A97718-549F-40F2-BE8D-64C699D2680F}" name="Extra2" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{9AE8E965-0B21-468D-814D-9FD22A09D2B0}" name="nom table" dataDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{908A4D0E-C232-43D4-BCF1-D888DBDD0BA1}" name="nom colonne" dataDxfId="56"/>
+    <tableColumn id="3" xr3:uid="{72BE23E7-4BEC-4486-9A9D-516D8C1E60E1}" name="type" dataDxfId="55"/>
+    <tableColumn id="4" xr3:uid="{B71E94CD-95C7-4728-B535-41CEAFE3AE18}" name="Interclassement" dataDxfId="54"/>
+    <tableColumn id="5" xr3:uid="{A16B840B-0CE8-4726-972C-84FAE671FF92}" name="Attributs" dataDxfId="53"/>
+    <tableColumn id="6" xr3:uid="{79FE67FC-68D7-49FF-9EDC-88E046C1D212}" name="Null" dataDxfId="52"/>
+    <tableColumn id="7" xr3:uid="{2FF80A13-5FA3-49A7-BAB0-B732F814C1F4}" name="Valeur par défaut" dataDxfId="51"/>
+    <tableColumn id="8" xr3:uid="{1569FBC2-03BC-4E35-8636-E0826A5659BE}" name="(clé étrangère) Pointe vers" dataDxfId="50"/>
+    <tableColumn id="9" xr3:uid="{FD191C2C-D2F4-46AF-8433-18181AB3F030}" name="Est pointé depuis" dataDxfId="49"/>
+    <tableColumn id="10" xr3:uid="{05A97718-549F-40F2-BE8D-64C699D2680F}" name="Extra2" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B2130637-D823-466F-9E7C-A0B2974DBAB9}" name="Tableau262" displayName="Tableau262" ref="B33:K37" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B2130637-D823-466F-9E7C-A0B2974DBAB9}" name="Tableau262" displayName="Tableau262" ref="B33:K37" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
   <autoFilter ref="B33:K37" xr:uid="{B2130637-D823-466F-9E7C-A0B2974DBAB9}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{3B8F7F72-A334-4A49-BEE0-D13E23F3E3CC}" name="nom table" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{AEB3CC68-42FB-4348-BC29-FF88B0E3E32F}" name="nom colonne" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{FDB27E46-F3D7-4AD3-8C8E-38CCF3BACC40}" name="type" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{586C31D4-499E-4F13-B384-12E98B0846B0}" name="Interclassement" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{F8C8E00A-85CA-4E4D-A981-2D224A007457}" name="Attributs" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{CC2360D5-0BE6-46A3-8F52-92DAC95DA8C5}" name="Null" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{220E2022-11C7-4541-94F2-61F18AA75412}" name="Valeur par défaut" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{3D6C0E02-E889-4F1E-B8E8-0E6D79A326CB}" name="(clé étrangère) Pointe vers" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{1923CC31-7C4A-4F33-AF1C-81A17636208D}" name="Est pointé depuis" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{CEBB73E6-8AD0-4EB7-A512-9EBF052F98A0}" name="Extra2" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{3B8F7F72-A334-4A49-BEE0-D13E23F3E3CC}" name="nom table" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{AEB3CC68-42FB-4348-BC29-FF88B0E3E32F}" name="nom colonne" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{FDB27E46-F3D7-4AD3-8C8E-38CCF3BACC40}" name="type" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{586C31D4-499E-4F13-B384-12E98B0846B0}" name="Interclassement" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{F8C8E00A-85CA-4E4D-A981-2D224A007457}" name="Attributs" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{CC2360D5-0BE6-46A3-8F52-92DAC95DA8C5}" name="Null" dataDxfId="40"/>
+    <tableColumn id="7" xr3:uid="{220E2022-11C7-4541-94F2-61F18AA75412}" name="Valeur par défaut" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{3D6C0E02-E889-4F1E-B8E8-0E6D79A326CB}" name="(clé étrangère) Pointe vers" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{1923CC31-7C4A-4F33-AF1C-81A17636208D}" name="Est pointé depuis" dataDxfId="37"/>
+    <tableColumn id="10" xr3:uid="{CEBB73E6-8AD0-4EB7-A512-9EBF052F98A0}" name="Extra2" dataDxfId="36"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{4A46F6C2-25B0-4B2E-AFF2-D7A152F2D085}" name="Tableau2627" displayName="Tableau2627" ref="B40:K46" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{4A46F6C2-25B0-4B2E-AFF2-D7A152F2D085}" name="Tableau2627" displayName="Tableau2627" ref="B40:K46" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
   <autoFilter ref="B40:K46" xr:uid="{4A46F6C2-25B0-4B2E-AFF2-D7A152F2D085}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{B0196D0D-4EE9-4669-B58D-8221FA31729C}" name="nom table" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{339D5E01-998A-4D41-A541-124611D984EA}" name="nom colonne" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{E4968142-9B29-4C13-95AE-65FAABE5E344}" name="type" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{3F85CB82-F3FF-42F2-9F2F-B6D9B52BE9EA}" name="Interclassement" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{FC709251-65F8-45D7-908E-93A303D53C8C}" name="Attributs" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{61A4ECD6-1666-4AB5-9F5A-8171206B2065}" name="Null" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{3B57F620-CD26-4A82-91BD-8477C3480807}" name="Valeur par défaut" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{FB067A86-938C-43E4-B4EE-E7F0FEF35F81}" name="(clé étrangère) Pointe vers" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{F44CB662-EB1D-44EA-B201-869A9416FCED}" name="Est pointé depuis" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{EBA54CB5-27B4-49A3-8F65-D5FD1AEA140D}" name="Extra2" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{B0196D0D-4EE9-4669-B58D-8221FA31729C}" name="nom table" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{339D5E01-998A-4D41-A541-124611D984EA}" name="nom colonne" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{E4968142-9B29-4C13-95AE-65FAABE5E344}" name="type" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{3F85CB82-F3FF-42F2-9F2F-B6D9B52BE9EA}" name="Interclassement" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{FC709251-65F8-45D7-908E-93A303D53C8C}" name="Attributs" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{61A4ECD6-1666-4AB5-9F5A-8171206B2065}" name="Null" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{3B57F620-CD26-4A82-91BD-8477C3480807}" name="Valeur par défaut" dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{FB067A86-938C-43E4-B4EE-E7F0FEF35F81}" name="(clé étrangère) Pointe vers" dataDxfId="26"/>
+    <tableColumn id="9" xr3:uid="{F44CB662-EB1D-44EA-B201-869A9416FCED}" name="Est pointé depuis" dataDxfId="25"/>
+    <tableColumn id="10" xr3:uid="{EBA54CB5-27B4-49A3-8F65-D5FD1AEA140D}" name="Extra2" dataDxfId="24"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{767D7972-5DD0-47AC-A7DF-73E3E15C2A91}" name="Tableau2628" displayName="Tableau2628" ref="B49:K53" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+  <autoFilter ref="B49:K53" xr:uid="{767D7972-5DD0-47AC-A7DF-73E3E15C2A91}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{A186B227-DE2A-4DE4-A63B-44AA0250DE59}" name="nom table" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{9FC49BD4-36EE-428D-BD38-EBD461FAF1D8}" name="nom colonne" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{63F5F96C-9FE7-4A91-86C0-06620BC64DCA}" name="type" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{7CE33D33-D949-4B87-A293-A4AB9CF38F09}" name="Interclassement" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{A22B38A6-E6D3-4DC8-B05E-9402B4FBFF93}" name="Attributs" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{59BC56B6-841B-4091-AEAA-FF86BDAC6244}" name="Null" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{051CDA4E-61B7-41B7-994C-CC0DAC2B863B}" name="Valeur par défaut" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{C24E4BBB-D77D-4036-B895-94C02F44CF9D}" name="(clé étrangère) Pointe vers" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{8F590626-51EC-47B9-9BFC-35604A9C7D51}" name="Est pointé depuis" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{59BAAB00-C3AD-4012-93FD-2DA9769878E1}" name="Extra2" dataDxfId="12"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{60957CD5-D4ED-462F-8DF1-FF1700138EA3}" name="Tableau26279" displayName="Tableau26279" ref="B56:K61" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="B56:K61" xr:uid="{60957CD5-D4ED-462F-8DF1-FF1700138EA3}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{97561619-A00F-413D-B3EC-639244964255}" name="nom table" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{2F0E1888-0DAF-4D60-974D-DD1498E7CCFA}" name="nom colonne" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{BE1E65D2-F1EB-4EDD-87B9-7CA71FB43BFC}" name="type" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{2297DC35-89FA-4783-AA62-DA603E76183A}" name="Interclassement" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{A4D36A61-BA5D-497E-A46B-73C03F7B07F2}" name="Attributs" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{D96F9211-EB4A-4411-B330-C6BD65A409CE}" name="Null" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{E66369E2-F9CD-4634-8A48-D13D29D10F5E}" name="Valeur par défaut" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{620CD3C6-BC12-4A1C-BB4F-B9E6F5F23510}" name="(clé étrangère) Pointe vers" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{E89A295A-53CA-4215-8B86-709CA04A7223}" name="Est pointé depuis" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{AB5EF894-9442-48DC-AC3A-56442E34ACBA}" name="Extra2" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -934,7 +1060,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{540E0E48-FC0C-42DF-90F9-8F82C39FB181}">
-  <dimension ref="B2:K46"/>
+  <dimension ref="B2:K61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="1"/>
@@ -1425,7 +1551,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="45" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>33</v>
       </c>
@@ -1445,7 +1571,7 @@
         <v>11</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>29</v>
@@ -1588,7 +1714,7 @@
         <v>11</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>29</v>
@@ -1659,7 +1785,7 @@
     </row>
     <row r="39" spans="2:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -1705,10 +1831,10 @@
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>5</v>
@@ -1728,7 +1854,7 @@
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>48</v>
@@ -1746,15 +1872,15 @@
         <v>11</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>13</v>
@@ -1771,7 +1897,7 @@
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>17</v>
@@ -1791,7 +1917,7 @@
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>18</v>
@@ -1811,10 +1937,10 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>37</v>
@@ -1826,8 +1952,294 @@
         <v>11</v>
       </c>
     </row>
+    <row r="48" spans="2:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B49" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B51" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B52" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B53" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" s="2"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
+    </row>
+    <row r="56" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B56" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G56" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B57" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B58" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B59" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B60" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G60" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H60" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B61" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G61" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H61" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="B48:K48"/>
+    <mergeCell ref="B55:K55"/>
     <mergeCell ref="B39:K39"/>
     <mergeCell ref="B24:K24"/>
     <mergeCell ref="B18:K18"/>
@@ -1836,13 +2248,15 @@
     <mergeCell ref="B32:K32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="6">
+  <tableParts count="8">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
     <tablePart r:id="rId5"/>
     <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
+    <tablePart r:id="rId8"/>
   </tableParts>
 </worksheet>
 </file>
--- a/src/assets/schoolDesk/bdd/bdd build.xlsx
+++ b/src/assets/schoolDesk/bdd/bdd build.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MAMP\htdocs\Rugby-Academy\src\assets\schoolDesk\bdd\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00BB3908-7EC2-4F9B-96F0-7041F7D86A9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDA4026A-24E4-4BC4-88FF-33D94949F01E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{F8B8C4F5-9CBE-45C8-9BFD-685DE0AE8ED2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="85">
   <si>
     <t>role</t>
   </si>
@@ -177,9 +177,6 @@
     <t>user_role : ligne role_id</t>
   </si>
   <si>
-    <t>user_role : ligne user_id</t>
-  </si>
-  <si>
     <t xml:space="preserve">trombinoscope_group </t>
   </si>
   <si>
@@ -217,17 +214,92 @@
   </si>
   <si>
     <t>TEXT</t>
+  </si>
+  <si>
+    <t>structure_group : ligne groupe_id</t>
+  </si>
+  <si>
+    <t>structure_card : ligne groupe_id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">actu_post </t>
+  </si>
+  <si>
+    <t>post_id</t>
+  </si>
+  <si>
+    <t>content</t>
+  </si>
+  <si>
+    <t>created_at</t>
+  </si>
+  <si>
+    <t>user : ligne user_id</t>
+  </si>
+  <si>
+    <t>actu_post_image</t>
+  </si>
+  <si>
+    <t>image_id</t>
+  </si>
+  <si>
+    <t>image_data</t>
+  </si>
+  <si>
+    <t>BLOB</t>
+  </si>
+  <si>
+    <t>actu_post : ligne post_id</t>
+  </si>
+  <si>
+    <t>actu_post_video</t>
+  </si>
+  <si>
+    <t>video_id</t>
+  </si>
+  <si>
+    <t>video_data</t>
+  </si>
+  <si>
+    <t>actu_comment</t>
+  </si>
+  <si>
+    <t>comment_id</t>
+  </si>
+  <si>
+    <t>TIMESTAMP</t>
+  </si>
+  <si>
+    <t>CURRENT_TIMESTAMP</t>
+  </si>
+  <si>
+    <t>user_role : ligne user_id
+actu_post : ligne user_id
+actu_comment : ligne user_id</t>
+  </si>
+  <si>
+    <t>actu_post_like</t>
+  </si>
+  <si>
+    <t>like_id</t>
+  </si>
+  <si>
+    <t>like_status</t>
+  </si>
+  <si>
+    <t>ENUM('like', 'dislike')</t>
   </si>
   <si>
     <t>user_role : ligne club_id
 trombinoscope_group : ligne club_id
-structure_group  : ligne club_id</t>
-  </si>
-  <si>
-    <t>structure_group : ligne groupe_id</t>
-  </si>
-  <si>
-    <t>structure_card : ligne groupe_id</t>
+structure_group  : ligne club_id
+actu_post : ligne club_id
+actu_post_like : ligne club_id</t>
+  </si>
+  <si>
+    <t>actu_post_image : ligne post_id
+actu_comment : ligne post_id
+actu_post_like : ligne post_id</t>
   </si>
 </sst>
 </file>
@@ -289,7 +361,187 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="96">
+  <dxfs count="156">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -592,152 +844,247 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F7B9363E-452E-4289-93FC-70886BD6D8FB}" name="Tableau2" displayName="Tableau2" ref="B3:K5" totalsRowShown="0" headerRowDxfId="95" dataDxfId="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{F7B9363E-452E-4289-93FC-70886BD6D8FB}" name="Tableau2" displayName="Tableau2" ref="B3:K5" totalsRowShown="0" headerRowDxfId="155" dataDxfId="154">
   <autoFilter ref="B3:K5" xr:uid="{F7B9363E-452E-4289-93FC-70886BD6D8FB}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{DB4C2CD3-3231-4168-9A87-457D5664083E}" name="nom table" dataDxfId="93"/>
-    <tableColumn id="2" xr3:uid="{2192C049-1AEB-4E35-A091-A07CC91CD244}" name="nom colonne" dataDxfId="92"/>
-    <tableColumn id="3" xr3:uid="{F58F956B-23A5-44DC-B56B-F9B8C56B2423}" name="type" dataDxfId="91"/>
-    <tableColumn id="4" xr3:uid="{85757BEB-9E58-4E89-80B5-049A5B671907}" name="Interclassement" dataDxfId="90"/>
-    <tableColumn id="5" xr3:uid="{AAA0C635-0F93-4AF6-B139-362C2718F431}" name="Attributs" dataDxfId="89"/>
-    <tableColumn id="6" xr3:uid="{077C9FE2-0A59-49FB-9CC1-7902F968C636}" name="Null" dataDxfId="88"/>
-    <tableColumn id="7" xr3:uid="{D3497013-3EF1-42FD-8060-211DD3868C03}" name="Valeur par défaut" dataDxfId="87"/>
-    <tableColumn id="8" xr3:uid="{407A762B-C81E-4389-87AC-0043C1E43AA0}" name="(clé étrangère) Pointe vers" dataDxfId="86"/>
-    <tableColumn id="9" xr3:uid="{5B40F928-777F-4FB3-BCBE-58A5C477C95E}" name="Est pointé depuis" dataDxfId="85"/>
-    <tableColumn id="10" xr3:uid="{EE04D510-1207-48EF-ADAB-C32FA84C32DF}" name="Extra2" dataDxfId="84"/>
+    <tableColumn id="1" xr3:uid="{DB4C2CD3-3231-4168-9A87-457D5664083E}" name="nom table" dataDxfId="153"/>
+    <tableColumn id="2" xr3:uid="{2192C049-1AEB-4E35-A091-A07CC91CD244}" name="nom colonne" dataDxfId="152"/>
+    <tableColumn id="3" xr3:uid="{F58F956B-23A5-44DC-B56B-F9B8C56B2423}" name="type" dataDxfId="151"/>
+    <tableColumn id="4" xr3:uid="{85757BEB-9E58-4E89-80B5-049A5B671907}" name="Interclassement" dataDxfId="150"/>
+    <tableColumn id="5" xr3:uid="{AAA0C635-0F93-4AF6-B139-362C2718F431}" name="Attributs" dataDxfId="149"/>
+    <tableColumn id="6" xr3:uid="{077C9FE2-0A59-49FB-9CC1-7902F968C636}" name="Null" dataDxfId="148"/>
+    <tableColumn id="7" xr3:uid="{D3497013-3EF1-42FD-8060-211DD3868C03}" name="Valeur par défaut" dataDxfId="147"/>
+    <tableColumn id="8" xr3:uid="{407A762B-C81E-4389-87AC-0043C1E43AA0}" name="(clé étrangère) Pointe vers" dataDxfId="146"/>
+    <tableColumn id="9" xr3:uid="{5B40F928-777F-4FB3-BCBE-58A5C477C95E}" name="Est pointé depuis" dataDxfId="145"/>
+    <tableColumn id="10" xr3:uid="{EE04D510-1207-48EF-ADAB-C32FA84C32DF}" name="Extra2" dataDxfId="144"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{77153A55-78E2-4F48-A969-D74E0E5FE194}" name="Tableau262791011" displayName="Tableau262791011" ref="B72:K75" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
+  <autoFilter ref="B72:K75" xr:uid="{77153A55-78E2-4F48-A969-D74E0E5FE194}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{36EAD63B-FC1D-49DB-99B0-33FA2E1879CA}" name="nom table" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{563B6743-9224-45E8-8567-70C4BFB9D3F4}" name="nom colonne" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{1AE0DA54-AC64-4BA4-9FBC-E42713A53FCB}" name="type" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{22C0F71D-BBEF-46F3-97DC-EC53D5A47F4A}" name="Interclassement" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{6877C14C-D5DC-4015-A928-A03278469461}" name="Attributs" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{A968F6C0-9780-4A1C-9422-AA1EA008BC28}" name="Null" dataDxfId="40"/>
+    <tableColumn id="7" xr3:uid="{F16736E4-1E43-4538-9F8E-9E84662F45C1}" name="Valeur par défaut" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{20EE967F-2960-4C86-B3E6-973D9EA27E6C}" name="(clé étrangère) Pointe vers" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{15A95183-19C7-4399-A116-56AA48613525}" name="Est pointé depuis" dataDxfId="37"/>
+    <tableColumn id="10" xr3:uid="{3DFE785B-9424-4411-856C-FB248F435474}" name="Extra2" dataDxfId="36"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table11.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{0D417D68-FAED-4A64-9457-3F258FFD8566}" name="Tableau26279101112" displayName="Tableau26279101112" ref="B78:K81" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
+  <autoFilter ref="B78:K81" xr:uid="{0D417D68-FAED-4A64-9457-3F258FFD8566}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{DE5C26FA-EB8F-4F7B-BC85-ECDAD037C93D}" name="nom table" dataDxfId="33"/>
+    <tableColumn id="2" xr3:uid="{0D01C380-82F7-4633-8F47-900330CE4EDD}" name="nom colonne" dataDxfId="32"/>
+    <tableColumn id="3" xr3:uid="{C103CA1F-4D4C-4F9A-8346-59D6F03E0E98}" name="type" dataDxfId="31"/>
+    <tableColumn id="4" xr3:uid="{F2F978B2-E862-43BA-84AB-0C964710039E}" name="Interclassement" dataDxfId="30"/>
+    <tableColumn id="5" xr3:uid="{6A531995-A115-4A09-937A-8BC480407D34}" name="Attributs" dataDxfId="29"/>
+    <tableColumn id="6" xr3:uid="{A5D0F118-5EBE-463D-9BC9-45AFAEE2DB96}" name="Null" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{E41ABA07-430A-4B77-AF63-A990DE7ED86C}" name="Valeur par défaut" dataDxfId="27"/>
+    <tableColumn id="8" xr3:uid="{6855F94C-ADC8-4390-9A1F-38E7CEF04CC3}" name="(clé étrangère) Pointe vers" dataDxfId="26"/>
+    <tableColumn id="9" xr3:uid="{75F918A8-7F7A-42ED-ABD5-F018AEB6DDF5}" name="Est pointé depuis" dataDxfId="25"/>
+    <tableColumn id="10" xr3:uid="{D53DAF44-E0A9-4DF2-A92D-7FCA03C28F9E}" name="Extra2" dataDxfId="24"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="12" xr:uid="{D3005A59-15D5-4E84-BF17-969554B7E945}" name="Tableau2627910111213" displayName="Tableau2627910111213" ref="B84:K89" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+  <autoFilter ref="B84:K89" xr:uid="{D3005A59-15D5-4E84-BF17-969554B7E945}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{139A8D0F-50DB-4EDB-8C6C-F901B2685FC0}" name="nom table" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{32438CB9-D8CC-4F71-8E14-2A454BFE68EA}" name="nom colonne" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{5AB4519F-CEDA-4FFF-8BAC-B769200FC982}" name="type" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{8502E405-E704-4E54-9914-68FCBED8D24C}" name="Interclassement" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{230E103F-B7FF-4ADF-81EB-A69ED24C7F18}" name="Attributs" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{1E9FA3A5-F804-4F4B-81AB-78B37379E00E}" name="Null" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{436D2CE1-411E-49D1-BB1A-2144913B956F}" name="Valeur par défaut" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{602F7E38-E2D1-4677-B470-58BA3E13E615}" name="(clé étrangère) Pointe vers" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{B6C6E224-1DAD-465D-A550-3011FB3506E0}" name="Est pointé depuis" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{993E09C6-4275-452E-8142-8D6AC5C63D2C}" name="Extra2" dataDxfId="12"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="13" xr:uid="{458099BE-C937-4242-903C-A9051F70F6DE}" name="Tableau262791011121314" displayName="Tableau262791011121314" ref="B92:K97" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="B92:K97" xr:uid="{458099BE-C937-4242-903C-A9051F70F6DE}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{288FEE95-3261-4A32-BB87-3460782358CE}" name="nom table" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{4C7033DB-1FE8-4EBA-81A4-0AC0F3568EB5}" name="nom colonne" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{8213DB46-C257-46BA-9196-993CA61871CF}" name="type" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{5526F0C9-D50F-45CD-B8DE-AF4CB0377388}" name="Interclassement" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{C11515B6-A95D-41FA-A4CC-C604F9D90C58}" name="Attributs" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{FFBD0CA4-2A3B-4290-A7D0-66F20E1A1EFF}" name="Null" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{893C064B-9E84-47AB-80FE-E3F44BDD068D}" name="Valeur par défaut" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{B7D7B0D9-1FFA-41EA-AA8C-0858D78C3E3A}" name="(clé étrangère) Pointe vers" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{6551CC92-9618-438D-B8A9-B725DC00CB9F}" name="Est pointé depuis" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{9B0AFF1D-623B-4B94-A984-1D68CCB3EC3D}" name="Extra2" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A2B3D216-B0BE-46DB-98BB-EBFCF643F6EF}" name="Tableau24" displayName="Tableau24" ref="B8:K16" totalsRowShown="0" headerRowDxfId="83" dataDxfId="82">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{A2B3D216-B0BE-46DB-98BB-EBFCF643F6EF}" name="Tableau24" displayName="Tableau24" ref="B8:K16" totalsRowShown="0" headerRowDxfId="143" dataDxfId="142">
   <autoFilter ref="B8:K16" xr:uid="{A2B3D216-B0BE-46DB-98BB-EBFCF643F6EF}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{15666A47-A6B0-4E0A-91AE-FB891679101B}" name="nom table" dataDxfId="81"/>
-    <tableColumn id="2" xr3:uid="{DFE8A646-5A6E-4382-A318-898309162AC6}" name="nom colonne" dataDxfId="80"/>
-    <tableColumn id="3" xr3:uid="{8161E4A6-BFC8-48E5-A144-897DC62F3CD6}" name="type" dataDxfId="79"/>
-    <tableColumn id="4" xr3:uid="{3F224333-E92F-4D3F-A895-7E8F8E63E833}" name="Interclassement" dataDxfId="78"/>
-    <tableColumn id="5" xr3:uid="{DADBA23C-D744-4CAA-8819-137469AF5DF5}" name="Attributs" dataDxfId="77"/>
-    <tableColumn id="6" xr3:uid="{7B36E0F4-12E1-4F86-BC0D-560A0F7ADA4A}" name="Null" dataDxfId="76"/>
-    <tableColumn id="7" xr3:uid="{099F1013-33FB-4C84-9B53-8F62353BADAC}" name="Valeur par défaut" dataDxfId="75"/>
-    <tableColumn id="8" xr3:uid="{83232AFE-D729-4180-B284-3864FAEC2CD3}" name="(clé étrangère) Pointe vers" dataDxfId="74"/>
-    <tableColumn id="9" xr3:uid="{944CFF04-1EFE-4C94-BF04-99759F88C2DC}" name="Est pointé depuis" dataDxfId="73"/>
-    <tableColumn id="10" xr3:uid="{6882D6F5-62FC-400C-AC09-0100987362DD}" name="Extra2" dataDxfId="72"/>
+    <tableColumn id="1" xr3:uid="{15666A47-A6B0-4E0A-91AE-FB891679101B}" name="nom table" dataDxfId="141"/>
+    <tableColumn id="2" xr3:uid="{DFE8A646-5A6E-4382-A318-898309162AC6}" name="nom colonne" dataDxfId="140"/>
+    <tableColumn id="3" xr3:uid="{8161E4A6-BFC8-48E5-A144-897DC62F3CD6}" name="type" dataDxfId="139"/>
+    <tableColumn id="4" xr3:uid="{3F224333-E92F-4D3F-A895-7E8F8E63E833}" name="Interclassement" dataDxfId="138"/>
+    <tableColumn id="5" xr3:uid="{DADBA23C-D744-4CAA-8819-137469AF5DF5}" name="Attributs" dataDxfId="137"/>
+    <tableColumn id="6" xr3:uid="{7B36E0F4-12E1-4F86-BC0D-560A0F7ADA4A}" name="Null" dataDxfId="136"/>
+    <tableColumn id="7" xr3:uid="{099F1013-33FB-4C84-9B53-8F62353BADAC}" name="Valeur par défaut" dataDxfId="135"/>
+    <tableColumn id="8" xr3:uid="{83232AFE-D729-4180-B284-3864FAEC2CD3}" name="(clé étrangère) Pointe vers" dataDxfId="134"/>
+    <tableColumn id="9" xr3:uid="{944CFF04-1EFE-4C94-BF04-99759F88C2DC}" name="Est pointé depuis" dataDxfId="133"/>
+    <tableColumn id="10" xr3:uid="{6882D6F5-62FC-400C-AC09-0100987362DD}" name="Extra2" dataDxfId="132"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4988D469-AD98-46C4-88D3-4A641744DA50}" name="Tableau25" displayName="Tableau25" ref="B19:K22" totalsRowShown="0" headerRowDxfId="71" dataDxfId="70">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{4988D469-AD98-46C4-88D3-4A641744DA50}" name="Tableau25" displayName="Tableau25" ref="B19:K22" totalsRowShown="0" headerRowDxfId="131" dataDxfId="130">
   <autoFilter ref="B19:K22" xr:uid="{4988D469-AD98-46C4-88D3-4A641744DA50}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{02BB2D94-0C11-489C-A941-D935E51FCC2F}" name="nom table" dataDxfId="69"/>
-    <tableColumn id="2" xr3:uid="{03FD9E41-50D8-4886-B21D-58D99087C0C9}" name="nom colonne" dataDxfId="68"/>
-    <tableColumn id="3" xr3:uid="{114AB77E-D5C9-4EDA-92E5-F821A0B6289B}" name="type" dataDxfId="67"/>
-    <tableColumn id="4" xr3:uid="{35482F0D-880F-41BE-9603-A05C9DCE73A9}" name="Interclassement" dataDxfId="66"/>
-    <tableColumn id="5" xr3:uid="{A0A47C94-BF2A-4E1E-A050-21842B13386A}" name="Attributs" dataDxfId="65"/>
-    <tableColumn id="6" xr3:uid="{F45F8180-9A05-49A5-8C33-B48EBE3B0157}" name="Null" dataDxfId="64"/>
-    <tableColumn id="7" xr3:uid="{CBC3CADB-CB55-4F26-9EC5-DB274703AF01}" name="Valeur par défaut" dataDxfId="63"/>
-    <tableColumn id="8" xr3:uid="{A4F19A0E-1B3E-4E3B-88D9-7327DA24E71D}" name="(clé étrangère) Pointe vers" dataDxfId="62"/>
-    <tableColumn id="9" xr3:uid="{699699A2-A73C-4C59-8354-C04B358C6913}" name="Est pointé depuis" dataDxfId="61"/>
-    <tableColumn id="10" xr3:uid="{E8A1F3E0-9FFC-4D33-887C-6A0EFECEDE8B}" name="Extra2" dataDxfId="60"/>
+    <tableColumn id="1" xr3:uid="{02BB2D94-0C11-489C-A941-D935E51FCC2F}" name="nom table" dataDxfId="129"/>
+    <tableColumn id="2" xr3:uid="{03FD9E41-50D8-4886-B21D-58D99087C0C9}" name="nom colonne" dataDxfId="128"/>
+    <tableColumn id="3" xr3:uid="{114AB77E-D5C9-4EDA-92E5-F821A0B6289B}" name="type" dataDxfId="127"/>
+    <tableColumn id="4" xr3:uid="{35482F0D-880F-41BE-9603-A05C9DCE73A9}" name="Interclassement" dataDxfId="126"/>
+    <tableColumn id="5" xr3:uid="{A0A47C94-BF2A-4E1E-A050-21842B13386A}" name="Attributs" dataDxfId="125"/>
+    <tableColumn id="6" xr3:uid="{F45F8180-9A05-49A5-8C33-B48EBE3B0157}" name="Null" dataDxfId="124"/>
+    <tableColumn id="7" xr3:uid="{CBC3CADB-CB55-4F26-9EC5-DB274703AF01}" name="Valeur par défaut" dataDxfId="123"/>
+    <tableColumn id="8" xr3:uid="{A4F19A0E-1B3E-4E3B-88D9-7327DA24E71D}" name="(clé étrangère) Pointe vers" dataDxfId="122"/>
+    <tableColumn id="9" xr3:uid="{699699A2-A73C-4C59-8354-C04B358C6913}" name="Est pointé depuis" dataDxfId="121"/>
+    <tableColumn id="10" xr3:uid="{E8A1F3E0-9FFC-4D33-887C-6A0EFECEDE8B}" name="Extra2" dataDxfId="120"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{FCA9C960-1AA3-4F83-BE30-98ED09E60E09}" name="Tableau26" displayName="Tableau26" ref="B25:K30" totalsRowShown="0" headerRowDxfId="59" dataDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{FCA9C960-1AA3-4F83-BE30-98ED09E60E09}" name="Tableau26" displayName="Tableau26" ref="B25:K30" totalsRowShown="0" headerRowDxfId="119" dataDxfId="118">
   <autoFilter ref="B25:K30" xr:uid="{FCA9C960-1AA3-4F83-BE30-98ED09E60E09}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{9AE8E965-0B21-468D-814D-9FD22A09D2B0}" name="nom table" dataDxfId="57"/>
-    <tableColumn id="2" xr3:uid="{908A4D0E-C232-43D4-BCF1-D888DBDD0BA1}" name="nom colonne" dataDxfId="56"/>
-    <tableColumn id="3" xr3:uid="{72BE23E7-4BEC-4486-9A9D-516D8C1E60E1}" name="type" dataDxfId="55"/>
-    <tableColumn id="4" xr3:uid="{B71E94CD-95C7-4728-B535-41CEAFE3AE18}" name="Interclassement" dataDxfId="54"/>
-    <tableColumn id="5" xr3:uid="{A16B840B-0CE8-4726-972C-84FAE671FF92}" name="Attributs" dataDxfId="53"/>
-    <tableColumn id="6" xr3:uid="{79FE67FC-68D7-49FF-9EDC-88E046C1D212}" name="Null" dataDxfId="52"/>
-    <tableColumn id="7" xr3:uid="{2FF80A13-5FA3-49A7-BAB0-B732F814C1F4}" name="Valeur par défaut" dataDxfId="51"/>
-    <tableColumn id="8" xr3:uid="{1569FBC2-03BC-4E35-8636-E0826A5659BE}" name="(clé étrangère) Pointe vers" dataDxfId="50"/>
-    <tableColumn id="9" xr3:uid="{FD191C2C-D2F4-46AF-8433-18181AB3F030}" name="Est pointé depuis" dataDxfId="49"/>
-    <tableColumn id="10" xr3:uid="{05A97718-549F-40F2-BE8D-64C699D2680F}" name="Extra2" dataDxfId="48"/>
+    <tableColumn id="1" xr3:uid="{9AE8E965-0B21-468D-814D-9FD22A09D2B0}" name="nom table" dataDxfId="117"/>
+    <tableColumn id="2" xr3:uid="{908A4D0E-C232-43D4-BCF1-D888DBDD0BA1}" name="nom colonne" dataDxfId="116"/>
+    <tableColumn id="3" xr3:uid="{72BE23E7-4BEC-4486-9A9D-516D8C1E60E1}" name="type" dataDxfId="115"/>
+    <tableColumn id="4" xr3:uid="{B71E94CD-95C7-4728-B535-41CEAFE3AE18}" name="Interclassement" dataDxfId="114"/>
+    <tableColumn id="5" xr3:uid="{A16B840B-0CE8-4726-972C-84FAE671FF92}" name="Attributs" dataDxfId="113"/>
+    <tableColumn id="6" xr3:uid="{79FE67FC-68D7-49FF-9EDC-88E046C1D212}" name="Null" dataDxfId="112"/>
+    <tableColumn id="7" xr3:uid="{2FF80A13-5FA3-49A7-BAB0-B732F814C1F4}" name="Valeur par défaut" dataDxfId="111"/>
+    <tableColumn id="8" xr3:uid="{1569FBC2-03BC-4E35-8636-E0826A5659BE}" name="(clé étrangère) Pointe vers" dataDxfId="110"/>
+    <tableColumn id="9" xr3:uid="{FD191C2C-D2F4-46AF-8433-18181AB3F030}" name="Est pointé depuis" dataDxfId="109"/>
+    <tableColumn id="10" xr3:uid="{05A97718-549F-40F2-BE8D-64C699D2680F}" name="Extra2" dataDxfId="108"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B2130637-D823-466F-9E7C-A0B2974DBAB9}" name="Tableau262" displayName="Tableau262" ref="B33:K37" totalsRowShown="0" headerRowDxfId="47" dataDxfId="46">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B2130637-D823-466F-9E7C-A0B2974DBAB9}" name="Tableau262" displayName="Tableau262" ref="B33:K37" totalsRowShown="0" headerRowDxfId="107" dataDxfId="106">
   <autoFilter ref="B33:K37" xr:uid="{B2130637-D823-466F-9E7C-A0B2974DBAB9}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{3B8F7F72-A334-4A49-BEE0-D13E23F3E3CC}" name="nom table" dataDxfId="45"/>
-    <tableColumn id="2" xr3:uid="{AEB3CC68-42FB-4348-BC29-FF88B0E3E32F}" name="nom colonne" dataDxfId="44"/>
-    <tableColumn id="3" xr3:uid="{FDB27E46-F3D7-4AD3-8C8E-38CCF3BACC40}" name="type" dataDxfId="43"/>
-    <tableColumn id="4" xr3:uid="{586C31D4-499E-4F13-B384-12E98B0846B0}" name="Interclassement" dataDxfId="42"/>
-    <tableColumn id="5" xr3:uid="{F8C8E00A-85CA-4E4D-A981-2D224A007457}" name="Attributs" dataDxfId="41"/>
-    <tableColumn id="6" xr3:uid="{CC2360D5-0BE6-46A3-8F52-92DAC95DA8C5}" name="Null" dataDxfId="40"/>
-    <tableColumn id="7" xr3:uid="{220E2022-11C7-4541-94F2-61F18AA75412}" name="Valeur par défaut" dataDxfId="39"/>
-    <tableColumn id="8" xr3:uid="{3D6C0E02-E889-4F1E-B8E8-0E6D79A326CB}" name="(clé étrangère) Pointe vers" dataDxfId="38"/>
-    <tableColumn id="9" xr3:uid="{1923CC31-7C4A-4F33-AF1C-81A17636208D}" name="Est pointé depuis" dataDxfId="37"/>
-    <tableColumn id="10" xr3:uid="{CEBB73E6-8AD0-4EB7-A512-9EBF052F98A0}" name="Extra2" dataDxfId="36"/>
+    <tableColumn id="1" xr3:uid="{3B8F7F72-A334-4A49-BEE0-D13E23F3E3CC}" name="nom table" dataDxfId="105"/>
+    <tableColumn id="2" xr3:uid="{AEB3CC68-42FB-4348-BC29-FF88B0E3E32F}" name="nom colonne" dataDxfId="104"/>
+    <tableColumn id="3" xr3:uid="{FDB27E46-F3D7-4AD3-8C8E-38CCF3BACC40}" name="type" dataDxfId="103"/>
+    <tableColumn id="4" xr3:uid="{586C31D4-499E-4F13-B384-12E98B0846B0}" name="Interclassement" dataDxfId="102"/>
+    <tableColumn id="5" xr3:uid="{F8C8E00A-85CA-4E4D-A981-2D224A007457}" name="Attributs" dataDxfId="101"/>
+    <tableColumn id="6" xr3:uid="{CC2360D5-0BE6-46A3-8F52-92DAC95DA8C5}" name="Null" dataDxfId="100"/>
+    <tableColumn id="7" xr3:uid="{220E2022-11C7-4541-94F2-61F18AA75412}" name="Valeur par défaut" dataDxfId="99"/>
+    <tableColumn id="8" xr3:uid="{3D6C0E02-E889-4F1E-B8E8-0E6D79A326CB}" name="(clé étrangère) Pointe vers" dataDxfId="98"/>
+    <tableColumn id="9" xr3:uid="{1923CC31-7C4A-4F33-AF1C-81A17636208D}" name="Est pointé depuis" dataDxfId="97"/>
+    <tableColumn id="10" xr3:uid="{CEBB73E6-8AD0-4EB7-A512-9EBF052F98A0}" name="Extra2" dataDxfId="96"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{4A46F6C2-25B0-4B2E-AFF2-D7A152F2D085}" name="Tableau2627" displayName="Tableau2627" ref="B40:K46" totalsRowShown="0" headerRowDxfId="35" dataDxfId="34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{4A46F6C2-25B0-4B2E-AFF2-D7A152F2D085}" name="Tableau2627" displayName="Tableau2627" ref="B40:K46" totalsRowShown="0" headerRowDxfId="95" dataDxfId="94">
   <autoFilter ref="B40:K46" xr:uid="{4A46F6C2-25B0-4B2E-AFF2-D7A152F2D085}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{B0196D0D-4EE9-4669-B58D-8221FA31729C}" name="nom table" dataDxfId="33"/>
-    <tableColumn id="2" xr3:uid="{339D5E01-998A-4D41-A541-124611D984EA}" name="nom colonne" dataDxfId="32"/>
-    <tableColumn id="3" xr3:uid="{E4968142-9B29-4C13-95AE-65FAABE5E344}" name="type" dataDxfId="31"/>
-    <tableColumn id="4" xr3:uid="{3F85CB82-F3FF-42F2-9F2F-B6D9B52BE9EA}" name="Interclassement" dataDxfId="30"/>
-    <tableColumn id="5" xr3:uid="{FC709251-65F8-45D7-908E-93A303D53C8C}" name="Attributs" dataDxfId="29"/>
-    <tableColumn id="6" xr3:uid="{61A4ECD6-1666-4AB5-9F5A-8171206B2065}" name="Null" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{3B57F620-CD26-4A82-91BD-8477C3480807}" name="Valeur par défaut" dataDxfId="27"/>
-    <tableColumn id="8" xr3:uid="{FB067A86-938C-43E4-B4EE-E7F0FEF35F81}" name="(clé étrangère) Pointe vers" dataDxfId="26"/>
-    <tableColumn id="9" xr3:uid="{F44CB662-EB1D-44EA-B201-869A9416FCED}" name="Est pointé depuis" dataDxfId="25"/>
-    <tableColumn id="10" xr3:uid="{EBA54CB5-27B4-49A3-8F65-D5FD1AEA140D}" name="Extra2" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{B0196D0D-4EE9-4669-B58D-8221FA31729C}" name="nom table" dataDxfId="93"/>
+    <tableColumn id="2" xr3:uid="{339D5E01-998A-4D41-A541-124611D984EA}" name="nom colonne" dataDxfId="92"/>
+    <tableColumn id="3" xr3:uid="{E4968142-9B29-4C13-95AE-65FAABE5E344}" name="type" dataDxfId="91"/>
+    <tableColumn id="4" xr3:uid="{3F85CB82-F3FF-42F2-9F2F-B6D9B52BE9EA}" name="Interclassement" dataDxfId="90"/>
+    <tableColumn id="5" xr3:uid="{FC709251-65F8-45D7-908E-93A303D53C8C}" name="Attributs" dataDxfId="89"/>
+    <tableColumn id="6" xr3:uid="{61A4ECD6-1666-4AB5-9F5A-8171206B2065}" name="Null" dataDxfId="88"/>
+    <tableColumn id="7" xr3:uid="{3B57F620-CD26-4A82-91BD-8477C3480807}" name="Valeur par défaut" dataDxfId="87"/>
+    <tableColumn id="8" xr3:uid="{FB067A86-938C-43E4-B4EE-E7F0FEF35F81}" name="(clé étrangère) Pointe vers" dataDxfId="86"/>
+    <tableColumn id="9" xr3:uid="{F44CB662-EB1D-44EA-B201-869A9416FCED}" name="Est pointé depuis" dataDxfId="85"/>
+    <tableColumn id="10" xr3:uid="{EBA54CB5-27B4-49A3-8F65-D5FD1AEA140D}" name="Extra2" dataDxfId="84"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{767D7972-5DD0-47AC-A7DF-73E3E15C2A91}" name="Tableau2628" displayName="Tableau2628" ref="B49:K53" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{767D7972-5DD0-47AC-A7DF-73E3E15C2A91}" name="Tableau2628" displayName="Tableau2628" ref="B49:K53" totalsRowShown="0" headerRowDxfId="83" dataDxfId="82">
   <autoFilter ref="B49:K53" xr:uid="{767D7972-5DD0-47AC-A7DF-73E3E15C2A91}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{A186B227-DE2A-4DE4-A63B-44AA0250DE59}" name="nom table" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{9FC49BD4-36EE-428D-BD38-EBD461FAF1D8}" name="nom colonne" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{63F5F96C-9FE7-4A91-86C0-06620BC64DCA}" name="type" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{7CE33D33-D949-4B87-A293-A4AB9CF38F09}" name="Interclassement" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{A22B38A6-E6D3-4DC8-B05E-9402B4FBFF93}" name="Attributs" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{59BC56B6-841B-4091-AEAA-FF86BDAC6244}" name="Null" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{051CDA4E-61B7-41B7-994C-CC0DAC2B863B}" name="Valeur par défaut" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{C24E4BBB-D77D-4036-B895-94C02F44CF9D}" name="(clé étrangère) Pointe vers" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{8F590626-51EC-47B9-9BFC-35604A9C7D51}" name="Est pointé depuis" dataDxfId="13"/>
-    <tableColumn id="10" xr3:uid="{59BAAB00-C3AD-4012-93FD-2DA9769878E1}" name="Extra2" dataDxfId="12"/>
+    <tableColumn id="1" xr3:uid="{A186B227-DE2A-4DE4-A63B-44AA0250DE59}" name="nom table" dataDxfId="81"/>
+    <tableColumn id="2" xr3:uid="{9FC49BD4-36EE-428D-BD38-EBD461FAF1D8}" name="nom colonne" dataDxfId="80"/>
+    <tableColumn id="3" xr3:uid="{63F5F96C-9FE7-4A91-86C0-06620BC64DCA}" name="type" dataDxfId="79"/>
+    <tableColumn id="4" xr3:uid="{7CE33D33-D949-4B87-A293-A4AB9CF38F09}" name="Interclassement" dataDxfId="78"/>
+    <tableColumn id="5" xr3:uid="{A22B38A6-E6D3-4DC8-B05E-9402B4FBFF93}" name="Attributs" dataDxfId="77"/>
+    <tableColumn id="6" xr3:uid="{59BC56B6-841B-4091-AEAA-FF86BDAC6244}" name="Null" dataDxfId="76"/>
+    <tableColumn id="7" xr3:uid="{051CDA4E-61B7-41B7-994C-CC0DAC2B863B}" name="Valeur par défaut" dataDxfId="75"/>
+    <tableColumn id="8" xr3:uid="{C24E4BBB-D77D-4036-B895-94C02F44CF9D}" name="(clé étrangère) Pointe vers" dataDxfId="74"/>
+    <tableColumn id="9" xr3:uid="{8F590626-51EC-47B9-9BFC-35604A9C7D51}" name="Est pointé depuis" dataDxfId="73"/>
+    <tableColumn id="10" xr3:uid="{59BAAB00-C3AD-4012-93FD-2DA9769878E1}" name="Extra2" dataDxfId="72"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{60957CD5-D4ED-462F-8DF1-FF1700138EA3}" name="Tableau26279" displayName="Tableau26279" ref="B56:K61" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{60957CD5-D4ED-462F-8DF1-FF1700138EA3}" name="Tableau26279" displayName="Tableau26279" ref="B56:K61" totalsRowShown="0" headerRowDxfId="71" dataDxfId="70">
   <autoFilter ref="B56:K61" xr:uid="{60957CD5-D4ED-462F-8DF1-FF1700138EA3}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{97561619-A00F-413D-B3EC-639244964255}" name="nom table" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{2F0E1888-0DAF-4D60-974D-DD1498E7CCFA}" name="nom colonne" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{BE1E65D2-F1EB-4EDD-87B9-7CA71FB43BFC}" name="type" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{2297DC35-89FA-4783-AA62-DA603E76183A}" name="Interclassement" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{A4D36A61-BA5D-497E-A46B-73C03F7B07F2}" name="Attributs" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{D96F9211-EB4A-4411-B330-C6BD65A409CE}" name="Null" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{E66369E2-F9CD-4634-8A48-D13D29D10F5E}" name="Valeur par défaut" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{620CD3C6-BC12-4A1C-BB4F-B9E6F5F23510}" name="(clé étrangère) Pointe vers" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{E89A295A-53CA-4215-8B86-709CA04A7223}" name="Est pointé depuis" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{AB5EF894-9442-48DC-AC3A-56442E34ACBA}" name="Extra2" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{97561619-A00F-413D-B3EC-639244964255}" name="nom table" dataDxfId="69"/>
+    <tableColumn id="2" xr3:uid="{2F0E1888-0DAF-4D60-974D-DD1498E7CCFA}" name="nom colonne" dataDxfId="68"/>
+    <tableColumn id="3" xr3:uid="{BE1E65D2-F1EB-4EDD-87B9-7CA71FB43BFC}" name="type" dataDxfId="67"/>
+    <tableColumn id="4" xr3:uid="{2297DC35-89FA-4783-AA62-DA603E76183A}" name="Interclassement" dataDxfId="66"/>
+    <tableColumn id="5" xr3:uid="{A4D36A61-BA5D-497E-A46B-73C03F7B07F2}" name="Attributs" dataDxfId="65"/>
+    <tableColumn id="6" xr3:uid="{D96F9211-EB4A-4411-B330-C6BD65A409CE}" name="Null" dataDxfId="64"/>
+    <tableColumn id="7" xr3:uid="{E66369E2-F9CD-4634-8A48-D13D29D10F5E}" name="Valeur par défaut" dataDxfId="63"/>
+    <tableColumn id="8" xr3:uid="{620CD3C6-BC12-4A1C-BB4F-B9E6F5F23510}" name="(clé étrangère) Pointe vers" dataDxfId="62"/>
+    <tableColumn id="9" xr3:uid="{E89A295A-53CA-4215-8B86-709CA04A7223}" name="Est pointé depuis" dataDxfId="61"/>
+    <tableColumn id="10" xr3:uid="{AB5EF894-9442-48DC-AC3A-56442E34ACBA}" name="Extra2" dataDxfId="60"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{39346EEA-7E2E-4BBE-B295-79B9F088C6EF}" name="Tableau2627910" displayName="Tableau2627910" ref="B64:K69" totalsRowShown="0" headerRowDxfId="59" dataDxfId="58">
+  <autoFilter ref="B64:K69" xr:uid="{39346EEA-7E2E-4BBE-B295-79B9F088C6EF}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{EC7EB4E6-60A7-45E4-BF00-A5938209EAAC}" name="nom table" dataDxfId="57"/>
+    <tableColumn id="2" xr3:uid="{97D31175-957E-4CB0-AEDC-72210E84FD43}" name="nom colonne" dataDxfId="56"/>
+    <tableColumn id="3" xr3:uid="{4326343C-6FD3-4804-93EA-288E916E5659}" name="type" dataDxfId="55"/>
+    <tableColumn id="4" xr3:uid="{F7CD8B85-753A-4F3E-9AAD-78487C6DEB73}" name="Interclassement" dataDxfId="54"/>
+    <tableColumn id="5" xr3:uid="{B4136E8D-969C-43CD-81E6-FAA03035DE75}" name="Attributs" dataDxfId="53"/>
+    <tableColumn id="6" xr3:uid="{1C051A3D-2378-4A4A-B300-0999231CA40E}" name="Null" dataDxfId="52"/>
+    <tableColumn id="7" xr3:uid="{227B6EE0-C3B6-444B-B88D-613653CF7A1A}" name="Valeur par défaut" dataDxfId="51"/>
+    <tableColumn id="8" xr3:uid="{FB303D37-6D52-4B77-A16C-1C8ED31B75E0}" name="(clé étrangère) Pointe vers" dataDxfId="50"/>
+    <tableColumn id="9" xr3:uid="{6276B15F-98B0-4AA5-A955-C12CA65F7707}" name="Est pointé depuis" dataDxfId="49"/>
+    <tableColumn id="10" xr3:uid="{F86ADA47-9112-4ABE-8022-BC7383030E30}" name="Extra2" dataDxfId="48"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1060,12 +1407,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{540E0E48-FC0C-42DF-90F9-8F82C39FB181}">
-  <dimension ref="B2:K61"/>
+  <dimension ref="B2:K97"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="1"/>
     <col min="2" max="2" width="44.7109375" style="1" customWidth="1"/>
-    <col min="3" max="4" width="17.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="17.42578125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="26.140625" style="1" customWidth="1"/>
     <col min="5" max="5" width="20.28515625" style="1" customWidth="1"/>
     <col min="6" max="7" width="17.42578125" style="1" customWidth="1"/>
     <col min="8" max="8" width="22" style="1" customWidth="1"/>
@@ -1215,7 +1563,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:11" ht="45" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
@@ -1235,7 +1583,7 @@
         <v>11</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>29</v>
@@ -1551,7 +1899,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="45" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" ht="75" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
         <v>33</v>
       </c>
@@ -1571,7 +1919,7 @@
         <v>11</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>29</v>
@@ -1650,7 +1998,7 @@
     </row>
     <row r="32" spans="2:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
@@ -1696,10 +2044,10 @@
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>48</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>5</v>
@@ -1714,7 +2062,7 @@
         <v>11</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>29</v>
@@ -1722,7 +2070,7 @@
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>34</v>
@@ -1740,12 +2088,12 @@
         <v>11</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>35</v>
@@ -1765,10 +2113,10 @@
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>5</v>
@@ -1785,7 +2133,7 @@
     </row>
     <row r="39" spans="2:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" s="2"/>
@@ -1831,10 +2179,10 @@
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>5</v>
@@ -1854,10 +2202,10 @@
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>5</v>
@@ -1872,15 +2220,15 @@
         <v>11</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>13</v>
@@ -1897,7 +2245,7 @@
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>17</v>
@@ -1917,7 +2265,7 @@
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>18</v>
@@ -1937,10 +2285,10 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>37</v>
@@ -1954,7 +2302,7 @@
     </row>
     <row r="48" spans="2:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
@@ -2000,10 +2348,10 @@
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>5</v>
@@ -2018,7 +2366,7 @@
         <v>11</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K50" s="1" t="s">
         <v>29</v>
@@ -2026,7 +2374,7 @@
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>34</v>
@@ -2044,12 +2392,12 @@
         <v>11</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>35</v>
@@ -2069,10 +2417,10 @@
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D53" s="1" t="s">
         <v>5</v>
@@ -2089,7 +2437,7 @@
     </row>
     <row r="55" spans="2:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
@@ -2135,10 +2483,10 @@
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>5</v>
@@ -2158,10 +2506,10 @@
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>5</v>
@@ -2176,12 +2524,12 @@
         <v>11</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>35</v>
@@ -2201,13 +2549,13 @@
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>27</v>
@@ -2221,10 +2569,10 @@
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>37</v>
@@ -2236,19 +2584,707 @@
         <v>11</v>
       </c>
     </row>
+    <row r="63" spans="2:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B63" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" s="2"/>
+      <c r="E63" s="2"/>
+      <c r="F63" s="2"/>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B64" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="B65" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B66" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I66" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B67" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B68" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B69" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B71" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" s="2"/>
+      <c r="E71" s="2"/>
+      <c r="F71" s="2"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
+    </row>
+    <row r="72" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B72" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I72" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B73" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B74" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B75" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B77" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" s="2"/>
+      <c r="E77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="2"/>
+      <c r="K77" s="2"/>
+    </row>
+    <row r="78" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B78" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I78" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B79" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B80" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I80" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B81" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B83" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" s="2"/>
+      <c r="E83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
+      <c r="J83" s="2"/>
+      <c r="K83" s="2"/>
+    </row>
+    <row r="84" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B84" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B85" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B86" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I86" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B87" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B88" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B89" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="91" spans="2:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B91" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" s="2"/>
+      <c r="E91" s="2"/>
+      <c r="F91" s="2"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+      <c r="I91" s="2"/>
+      <c r="J91" s="2"/>
+      <c r="K91" s="2"/>
+    </row>
+    <row r="92" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B92" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I92" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B93" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B94" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I94" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B95" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B96" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="97" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B97" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="13">
+    <mergeCell ref="B77:K77"/>
+    <mergeCell ref="B83:K83"/>
+    <mergeCell ref="B91:K91"/>
+    <mergeCell ref="B7:K7"/>
+    <mergeCell ref="B2:K2"/>
+    <mergeCell ref="B32:K32"/>
+    <mergeCell ref="B63:K63"/>
+    <mergeCell ref="B71:K71"/>
     <mergeCell ref="B48:K48"/>
     <mergeCell ref="B55:K55"/>
     <mergeCell ref="B39:K39"/>
     <mergeCell ref="B24:K24"/>
     <mergeCell ref="B18:K18"/>
-    <mergeCell ref="B7:K7"/>
-    <mergeCell ref="B2:K2"/>
-    <mergeCell ref="B32:K32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="8">
+  <tableParts count="13">
     <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
@@ -2257,6 +3293,11 @@
     <tablePart r:id="rId6"/>
     <tablePart r:id="rId7"/>
     <tablePart r:id="rId8"/>
+    <tablePart r:id="rId9"/>
+    <tablePart r:id="rId10"/>
+    <tablePart r:id="rId11"/>
+    <tablePart r:id="rId12"/>
+    <tablePart r:id="rId13"/>
   </tableParts>
 </worksheet>
 </file>